--- a/01_경혈별_해부생리_분석보고서/GB_족소양담경/GB21_견정/GB21_견정_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/GB_족소양담경/GB21_견정/GB21_견정_해부생리_분석데이터.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_온톨로지_실체매핑" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +59,18 @@
       <b val="1"/>
       <color rgb="009C5700"/>
     </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -89,8 +100,14 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -112,11 +129,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,6 +164,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,7 +557,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -963,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1249,6 +1285,614 @@
       <c r="D13" t="inlineStr">
         <is>
           <t>WRITER_BRIEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>보고서 4·5-1·6-1·8절 (2026-10-23 검증)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>다른 도구가 넣은 FMA ID 3건 오기(7566·7334·7335), 원문에 없는 초음파 수치(흉막 20.5±3.2 mm 등)와 합성 초음파 그림</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FMA ID 정정(7597·27534·7319), 5-1절을 원문 확인 수치(1431 SND 38.08±6.42 mm, 1896 TI 1.54)로 교체, 점수 불변</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PubMed PMID 29507586(PMC5817322)·42500462; fma_query.py entity</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>교재 수록 용어</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>FMA 실체 ID</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>FMA 표준 라벨</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>대응 수준</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>출처 교재</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>신경 지배 / 상위 줄기 사슬</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>척수 분절</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>등세모근 (trapezius)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>FMA:9626</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Trapezius</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>공통교재 · 김재효</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>지배신경줄기: Anterior ramus of fourth cervical nerve → Cervical nerve
+지배신경줄기: Anterior ramus of third cervical nerve → Cervical nerve
+지배신경줄기: Spinal accessory nerve</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>C3, C4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>가시위근 (supraspinatus)</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>FMA:9629</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Supraspinatus</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>지배신경줄기: Suprascapular nerve</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>C5, C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>빗장위신경 (supraclavicular nerve)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>FMA:65414</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Supraclavicular nerve</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>공통교재 · 김재효</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>등쪽어깨신경 (dorsal scapular nerve)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>FMA:65279</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Dorsal scapular nerve</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>공통교재 · 김재효</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>줄기: Anterior ramus of fifth cervical nerve → Fifth cervical nerve</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>어깨위신경 (suprascapular nerve)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>FMA:37025</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Suprascapular nerve</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>가로목동ㆍ정맥 (transverse cervical artery and vein)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>FMA:10664</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Transverse cervical artery</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>공통교재 · 김재효</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>줄기: Thyrocervical artery → Subclavian artery</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>가로목동ㆍ정맥 (transverse cervical artery and vein)</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>FMA:50858</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Transverse cervical vein</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>공통교재 · 김재효</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>줄기: External jugular vein → Subclavian vein → Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>어깨위동ㆍ정맥 (suprascapular artery and vein)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>FMA:10663</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Suprascapular artery</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>줄기: Thyrocervical artery → Subclavian artery</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>어깨위동ㆍ정맥 (suprascapular artery and vein)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>FMA:14319</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Suprascapular vein</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>줄기: External jugular vein → Subclavian vein → Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>어깨올림근 (levator scapulae)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>FMA:32519</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Levator scapulae</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>지배신경줄기: Anterior ramus of third cervical nerve → Cervical nerve
+지배신경줄기: Anterior ramus of fourth cervical nerve → Cervical nerve
+지배신경줄기: Dorsal scapular nerve → Anterior ramus of fifth cervical nerve → Fifth cervical nerve</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>C3, C4, C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>목널판근 (splenius cervicis)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>FMA:22681</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Splenius cervicis</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>지배신경줄기: Lateral branch of posterior ramus of second cervical nerve → Posterior ramus of second cervical nerve → Cervical nerve
+지배신경줄기: Lateral branch of posterior ramus of third cervical nerve → Posterior ramus of third cervical nerve → Cervical nerve
+지배신경줄기: Lateral branch of posterior ramus of fourth cervical nerve → Posterior ramus of fourth cervical nerve → Cervical nerve
+지배신경줄기: Lateral branch of posterior ramus of fifth cervical nerve → Posterior ramus of fifth cervical nerve → Fifth cervical nerve
+지배신경줄기: Lateral branch of posterior ramus of sixth cervical nerve → Posterior ramus of sixth cervical nerve → Cervical nerve
+지배신경줄기: Lateral branch of posterior ramus of seventh cervical nerve → Posterior ramus of seventh cervical nerve → Cervical nerve
+지배신경줄기: Lateral branch of posterior ramus of eighth cervical nerve → Posterior ramus of eighth cervical nerve → Cervical nerve
+지배신경줄기: Lateral branch of posterior ramus of first thoracic nerve → Posterior ramus of first thoracic nerve → Thoracic nerve
+지배신경줄기: Lateral branch of posterior ramus of second thoracic nerve → Posterior ramus of second thoracic nerve → Thoracic nerve
+지배신경줄기: Lateral branch of posterior ramus of third thoracic nerve → Posterior ramus of third thoracic nerve → Thoracic nerve
+지배신경줄기: Lateral branch of posterior ramus of fourth thoracic nerve → Posterior ramus of fourth thoracic nerve → Thoracic nerve
+지배신경줄기: Lateral branch of posterior ramus of fifth thoracic nerve → Posterior ramus of fifth thoracic nerve → Thoracic nerve
+지배신경줄기: Lateral branch of posterior ramus of sixth thoracic nerve → Posterior ramus of sixth thoracic nerve → Thoracic nerve</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>C2, C3, C4, C5, C6, C7, C8, T1, T2, T3, T4, T5, T6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>더부신경 (accessory nerve)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>FMA:6720</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Spinal accessory nerve</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1933,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1623,7 +2266,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1957,7 +2599,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -2239,7 +2880,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -2508,7 +3148,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>

--- a/01_경혈별_해부생리_분석보고서/GB_족소양담경/GB21_견정/GB21_견정_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/GB_족소양담경/GB21_견정/GB21_견정_해부생리_분석데이터.xlsx
@@ -9,16 +9,18 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="종합분석요약" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문헌고증_DB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자입심도_고금비교" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="층위별_해부신경구조" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고대언어_현대매핑" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_ARI_정량평가표" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARI_v3.0" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Check" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_온톨로지_실체매핑" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문헌스크리닝_4대원전" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자입심도_고금비교" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="층위별_해부신경구조" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고대언어_현대매핑" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_ARI_정량평가표" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARI_v3.0" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기추론_TriTarget" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Check" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_온톨로지_실체매핑" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -147,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,6 +171,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -823,169 +831,254 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>일시</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>소스</t>
+          <t>채점자 A</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>채점자 B</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>수집</t>
+          <t>최종</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t>중복제거</t>
+          <t>Layer B 참조 ID</t>
         </is>
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>papers.id</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>쿼리</t>
+          <t>근거(A)</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>근거(B)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-04T09:51:47</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>pubmed</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B1-01, B2-07, B2-09, B2-10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1431, 1432, 1876</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>("GB21" OR "Jianjing" OR "肩井") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy)</t>
+          <t>GB21 표준 위치의 사체 국소해부·초음파 심도 실측으로 등세모근·피신경·흉막 거리 확인.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2대 교재 공통 구조(등세모근·빗장위신경·등쪽어깨신경·가로목동정맥) + GB21 특이 국소해부·안전심도 실측.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-04T09:51:47</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>openalex</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>B1-03, B3-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>doi_starts_with:10.13703,title_and_abstract.search:"Jianjing" OR "GB21" | doi_starts_with:10.13702,title_and_abstract.search:"Jianjing" OR "GB21" | has_doi:true</t>
+          <t>C3~C4 분절은 견항통과 정합, 난산·유옹과는 불일치.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>국소 견배통·경항강과 C3-C5 피절·근절 정합. 난산·乳痈 등 원격 주치와는 분절 불일치.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-04T09:51:47</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>crossref</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>B2-06, B3-06, B3-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jianjing acupuncture nerve reflex</t>
+          <t>일반 구심 섬유 기전 유추.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>GB21 특이 구심 섬유·수용체 연구 없음, 일반 유추.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-04T09:51:47</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
-      </c>
-      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>B3-07, B3-08, B3-11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>관문조절·DNIC 유추.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>일반 침 진통 중추 경로 유추.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="F5" t="n">
-        <v>27</v>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>B2-03, B2-04, B2-06, B3-11</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>근막 이완·진통 방향은 견배통 주치와 일치(유추).</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>견배통 완화 방향은 유추로 일치. 난산 자궁수축 효과는 원심 경로 근거 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>B4-04, B4-05</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1874, 1884, 1891, 1893</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>혈류 pilot 1편 및 다혈 배오 RCT; 혈위 특이성 미확립.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>인체 관찰 1편과 다혈 배합 임상 RCT만 있어 혈위 특이 인체 전환 근거가 불충분.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>판정: 미부합</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -999,314 +1092,337 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>위치</t>
+          <t>papers.id</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>원래 내용</t>
+          <t>연도</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t>바꾼 내용</t>
+          <t>저널</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>PMID</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>설계</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>용도</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>구판 v2.6 점수 고전 96.0 / WHO 94.0 (비교 불가)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1876</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARI v3.0 | ARI-Core 67.5 ± 1.2 (C) | SI 0 ⚠ | 잠정 가중치 0.40/0.35/0.25 | 민감도(등가중치): 65.6 (C, 등급 불변)</t>
+          <t>J Tradit Chin Med</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>final_GB21.json</t>
+          <t>Topography of acupoint Jianjing (GB 21).</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>15270272</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>인체 국소해부</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>① 실체·안전</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>최초 기술</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>《靈樞·根結》</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1431</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>《黄帝明堂经》 / 《甲乙经》 3:44</t>
+          <t>Evid Based Complement Alternat Med</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>针灸腧穴通考(下)_241-320.md 1228·1249행; 通鉴 86168행</t>
+          <t>Change of Safe Needling Depth at Acupoint GB21 according to Posture and Breathing</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10.1155/2018/2308102</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>해부·영상</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>① 실체·SI</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>通考 인용</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>古人取肩上陷者中, 今人取最高點… (가공)</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1432</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2018</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>삭제, 실제 구절(肺尖·气胸九成, 不可向前下方刺入) 수록</t>
+          <t>Eur J Integr Med</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>通考 1255·1376행</t>
+          <t>Determining maximal safe needling depth based on anthropometric measurements - Focusing on acupoint GB21</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10.1016/j.eujim.2018.05.006</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>해부·영상</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>① 실체·SI</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>이명</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>少陽</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1896</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2026</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>膊井, 膽肩井 (+肩解, 井)</t>
+          <t>Integr Med Res</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KJH 327행; 通鉴 二.别名</t>
+          <t>Quantifying the therapeutic index of acupoints using measurements of effective and hazardous depths</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>42500462</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10.1016/j.imr.2026.101305</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>해부·영상</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI 보조</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>千金 교정</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>누락</t>
-        </is>
+      <c r="A6" t="n">
+        <v>1874</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2007</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>在→及 오자 교정 수록</t>
+          <t>J Altern Complement Med</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>通考 1262~1268행</t>
+          <t>Noninvasive blood flow measurement over acupuncture points (Gb21): a pilot study.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>17309375</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10.1089/acm.2006.9149</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>인체 관찰(비RCT)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>⑥ / S_reflex</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>동의보감</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>金鍼, 원문 '妊婦禁針'</t>
-        </is>
+      <c r="A7" t="n">
+        <v>1884</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2026</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>禁鍼; DB 값 0(동인), 孕妇禁针은 類經圖翼</t>
+          <t>Zhongguo Zhen Jiu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>자침깊이 DB 326행; 通考 1384행</t>
+          <t>Bloodletting at guasha marks combined with acupuncture for cervical spondylotic radiculopathy ...</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>41558700</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20241126-k0001</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>인체 RCT(다혈 배합)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>⑥ 보조</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>안전성</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>고전 정위 폐첨 위험 없음; 8푼 45° 13.0mm 안전 확보(경계 15mm)</t>
-        </is>
+      <c r="A8" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2016</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>철회. SI 0 ⚠, 15mm 출처 없음, 8푼 직자 경계 초과</t>
+          <t>Zhongguo Zhen Jiu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>자침깊이 DB 326행; papers.id 1431,1432,1876</t>
+          <t>Acupuncture and moxibustion based on meridian differentiation for cervical spondylosis radiculopathy ...</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>29231452</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.2016.06.008</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>인체 RCT(다혈 배합)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>⑥ 보조</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>기전</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>경부 교감신경절–옥시토신–난산</t>
-        </is>
+      <c r="A9" t="n">
+        <v>1893</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2021</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>삭제(근거 없음)</t>
+          <t>Zhen Ci Yan Jiu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B-Check ⑤</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>주치</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P_single 0.92/0.88/0.75</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>삭제, 단독/배오 분류</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>证治通鉴 3726~3730행</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>분기</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>T1/T2 Δ&gt;15mm</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>철회, 단일 Target</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>通考 名实考; override_note</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>WHO GV14–acromion, 능형근, 留七呼, 존재하지 않는 xlsx명, 깨진 LaTeX</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>정정</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>通考 1236·1378행 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>주의</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>기존 시트(종합분석요약 등)는 구판 내용 그대로 보존됨</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>md 보고서가 정본</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>WRITER_BRIEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>보고서 4·5-1·6-1·8절 (2026-10-23 검증)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>다른 도구가 넣은 FMA ID 3건 오기(7566·7334·7335), 원문에 없는 초음파 수치(흉막 20.5±3.2 mm 등)와 합성 초음파 그림</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>FMA ID 정정(7597·27534·7319), 5-1절을 원문 확인 수치(1431 SND 38.08±6.42 mm, 1896 TI 1.54)로 교체, 점수 불변</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PubMed PMID 29507586(PMC5817322)·42500462; fma_query.py entity</t>
+          <t>Randomized controlled trial on cervical spondylotic radiculopathy of wind-cold-damp type ...</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>34970881</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10.13702/j.1000-0607.20210006</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>인체 RCT(다혈 배합)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>⑥ 보조</t>
         </is>
       </c>
     </row>
@@ -1316,6 +1432,526 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>중복제거</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>쿼리</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-04T09:51:47</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>("GB21" OR "Jianjing" OR "肩井") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-04T09:51:47</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Jianjing" OR "GB21" | doi_starts_with:10.13702,title_and_abstract.search:"Jianjing" OR "GB21" | has_doi:true</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-04T09:51:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Jianjing acupuncture nerve reflex</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-04T09:51:47</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>원래 내용</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>바꾼 내용</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>구판 v2.6 점수 고전 96.0 / WHO 94.0 (비교 불가)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ARI v3.0 | ARI-Core 67.5 ± 1.2 (C) | SI 0 ⚠ | 잠정 가중치 0.40/0.35/0.25 | 민감도(등가중치): 65.6 (C, 등급 불변)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>final_GB21.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>최초 기술</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>《靈樞·根結》</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>《黄帝明堂经》 / 《甲乙经》 3:44</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>针灸腧穴通考(下)_241-320.md 1228·1249행; 通鉴 86168행</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>通考 인용</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>古人取肩上陷者中, 今人取最高點… (가공)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>삭제, 실제 구절(肺尖·气胸九成, 不可向前下方刺入) 수록</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>通考 1255·1376행</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>이명</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>少陽</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>膊井, 膽肩井 (+肩解, 井)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KJH 327행; 通鉴 二.别名</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>千金 교정</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>누락</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>在→及 오자 교정 수록</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>通考 1262~1268행</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>동의보감</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>金鍼, 원문 '妊婦禁針'</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>禁鍼; DB 값 0(동인), 孕妇禁针은 類經圖翼</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>자침깊이 DB 326행; 通考 1384행</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>안전성</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>고전 정위 폐첨 위험 없음; 8푼 45° 13.0mm 안전 확보(경계 15mm)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>철회. SI 0 ⚠, 15mm 출처 없음, 8푼 직자 경계 초과</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>자침깊이 DB 326행; papers.id 1431,1432,1876</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>기전</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>경부 교감신경절–옥시토신–난산</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>삭제(근거 없음)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>B-Check ⑤</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>주치</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P_single 0.92/0.88/0.75</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>삭제, 단독/배오 분류</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>证治通鉴 3726~3730행</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T1/T2 Δ&gt;15mm</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>철회, 단일 Target</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>通考 名实考; override_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WHO GV14–acromion, 능형근, 留七呼, 존재하지 않는 xlsx명, 깨진 LaTeX</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>정정</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>通考 1236·1378행 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>기존 시트(종합분석요약 등)는 구판 내용 그대로 보존됨</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>md 보고서가 정본</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>WRITER_BRIEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>보고서 4·5-1·6-1·8절 (2026-10-23 검증)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>다른 도구가 넣은 FMA ID 3건 오기(7566·7334·7335), 원문에 없는 초음파 수치(흉막 20.5±3.2 mm 등)와 합성 초음파 그림</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FMA ID 정정(7597·27534·7319), 5-1절을 원문 확인 수치(1431 SND 38.08±6.42 mm, 1896 TI 1.54)로 교체, 점수 불변</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PubMed PMID 29507586(PMC5817322)·42500462; fma_query.py entity</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Framework 2.7.7 (2026-10-25)</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>3대 원전; Dual-Target "분기 철회(Δ≤15mm)"; S_orig④ 通考 교감; 证治通鉴 포인터 3726~3730행</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>4대 원전(经络通鉴 11·05·23·18·27·28·35·37편 행 추가 — 문헌스크리닝_4대원전 시트); Tri-Target 재점검 Target 1≡2≡3(쌍별 Δ≤10mm 추정, 분기 기준 Δ&gt;10mm) — 분기추론_TriTarget 시트; ④ 通考·经络通鉴 교감 재점검 불변; 证治通鉴 09편 L218~250·한글번역 L288~332로 포인터 갱신, 14편 L368·16편 L348 촉진 표현 추가; ARI 점수 불변</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>프레임워크 2.7.7–2.7.8; data/classics/中国针灸经络通鉴/ 각 편; data/classics/中国针灸证治通鉴/ 09·14·16편(+한글번역)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2240,6 +2876,510 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>원전</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>편·인용 문헌</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>파일 (내부 포인터)</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>행</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>원문 발췌</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>요지·판정</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>용도</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>11편 脉度·骨度与要穴 — 《甲乙经·肩凡二十八穴》 卷三</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_11_第贰编_第三篇_脉度、骨度与要穴.md</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>L984</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>肩井，在肩上陷者中，缺盆上大骨前，手少阳、阳维之会，刺入五分，灸三壮</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>정위·심도 문구 이문 없음</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>1절·3절; S_orig④ 재점검(불변)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>05편 经络专篇研究 — 《足臂十一脉灸经》 手太阳 "出肩外廉" 校注</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_05_第壹编_第三篇_经络专篇研究.md</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>L576</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>出肩脉处，约当肩井穴处。《灵枢·邪气脏腑病形》诊小肠、膀胱病之脉位有"肩上"一处，候该处络脉之坚实、陷下以诊病。《太平圣惠方》卷九十九载甄权针书谓"此肩井脉，足阳明之会，乃连入五脏"</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>肩脉 출처·肩上 진락처(경맥 진찰 부위, 혈위 정위 기술 아님); 甄权 足阳明之会</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>1절·2절(참고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>37편 脉名索引 — 肩脉</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_37_第伍编_附篇一_脉名索引.md</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>L123</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>◇肩脉 66 69 73 227 228 763 1109</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>맥명 색인</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>23편 手太阳 — 《素问·气府论》, 《太素·气府》 杨上善 注</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_23_第叁编_第六篇_手太阳经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>L262, L266</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>柱骨上陷者各一 / ［柱骨出陷者各一，］肩井二穴，八也</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>杨注 위치 동정(이명 아님), 陷者 = 촉진 표현</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>1절·2절·3절</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>18편 手阳明 — 《千金要方》·《千金翼方》 卷29·26 및 按</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_18_第叁编_第二篇_手阳明经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>L330, L353</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>《千金要方》、《千金翼方》将"肩窌、秉风、肩井、天窌"四穴……归入本经</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>귀경 차이(手阳明)</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>3절 Rank 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>27편 手少阳 — 按</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_27_第叁编_第十篇_手少阳经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>L339</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>…比《铜人腧穴针灸图经》以后诸书多了…肩井…</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>귀경 차이(手少阳 계열)</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>3절 Rank 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>28편 足少阳 — 《铜人》 卷一, 按</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_28_第叁编_第十一篇_足少阳经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>L345, L355</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>足少阳胆经左右凡八十六穴 … 肩井 … / 《甲乙经》、《千金要方》、《千金翼方》等书中，除下肢十四个腧穴明确为足少阳经的腧穴外，其余穴位并未明确归经</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>《铜人》부터 足少阳 귀경</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>2절·3절</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>35편 阴维脉与阳维脉 — 《针灸大成》 卷七, 按(《甲乙》 阳维 交会穴)</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_35_第肆编_第六篇_阴维脉与阳维脉.md</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>L167, L226</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>又与手足少阳、足阳明会于肩井 / 阳维交会穴有：金门、阳交、天髎、肩井…</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>교회 기재 차이</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>3절 Rank 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>09편 足少阳胆经 十一)肩井 (원문)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸证治通鉴/中国针灸证治通鉴_09_第壹编_第七篇_足少阳胆经_足厥阴肝经.md</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>L218~250</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>主肩背痹痛，臂不举，寒热凄索气上，不得眠卧 … 小结 …并谓"泻之，须更即生"，值得研究</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>구 포인터 "정제본 3726~3730행" 대체; 원문 "须更"</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>1절·9절</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>09편 한글번역</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸证治通鉴/中国针灸证治通鉴_09_第壹编_第七篇_足少阳胆经_足厥阴肝经_한글번역.md</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>L288~332</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>…“사하면 잠깐 사이에 곧 낳는다.(瀉之，須更即生)”라고 하였으니, 연구해 볼 만하다</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>기술은 한글번역 문장으로</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>14편 中风 — 《卫生宝鉴·中风刺法》 卷七</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸证治通鉴/中国针灸证治通鉴_14_第叁编_内科病症_四中风至八痉证.md</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>L368 (한글번역 L668)</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>肩井二穴，在肩上陷解中，缺盆上大骨前一寸半，以三指按取之，当其中指下陷中者是</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Target 2 촉진 표현(陷中)</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>1절·7절</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>16편 痹证·脚气 — 《补辑肘后方》 上卷</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸证治通鉴/中国针灸证治通鉴_16_第叁编_内科病症_十六痹证至二十一项背痛.md</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>L348 (한글번역 L505)</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>穴在两肩小近头凹处，指捏之，安令正得中穴耳</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Target 2 촉진 표현(凹處), 안쪽 치우침 시사(크기 미기재)</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>1절·7절</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2567,7 +3707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2848,7 +3988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3116,7 +4256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3560,7 +4700,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3604,7 +4744,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3625,7 +4765,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3646,7 +4786,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3667,7 +4807,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3688,7 +4828,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3709,7 +4849,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3730,7 +4870,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3751,12 +4891,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S_orig④ 通考 교감</t>
+          <t>S_orig④ 通考·经络通鉴 교감</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3768,11 +4908,16 @@
       <c r="E9" t="n">
         <v>87.5</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-25 经络通鉴 재점검(11편 L984 이문 없음, 18·28·35편 귀경·교회 차이) → 단계 이동 없음, 불변</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3787,7 +4932,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3802,7 +4947,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3822,7 +4967,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3844,7 +4989,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3864,7 +5009,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3886,7 +5031,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3906,7 +5051,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3928,7 +5073,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3945,7 +5090,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3955,19 +5100,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>철회(Δ≤15mm)</t>
+          <t>Target 1≡2≡3 (쌍별 Δ ≤ 10mm 추정, 분기 없음)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>분기 해제: 두 채점자 모두 고전(明堂·甲乙 '在肩上陷者中, 缺盆上, 大骨前')과 WHO 정위의 차이가 Δ≤15mm임을 확인(A: 보고서 도식상 ±1cm, B: 《针灸腧穴通考》가 고전 기술을 대추–견봉 중점으로 해석). 정본 Rank 5 분기 기준 미충족 → 단일 Target(고전=WHO)으로 조정하고 WHO 정위 채점(T2)을 최종값으로 채택. 참고: 고전 정위 별도 채점값 A 62.5/50/50/0, B 68.75/50/50/0. S_safety 0은 자침깊이 DB 동의보감 '0'(금침) 근거로 두 채점자 일치 → ⚠.</t>
+          <t>2026-10-25 Tri-Target 재점검(분기추론_TriTarget 시트). 이전 비고: 분기 해제: 두 채점자 모두 고전(明堂·甲乙 '在肩上陷者中, 缺盆上, 大骨前')과 WHO 정위의 차이가 Δ≤15mm임을 확인(A: 보고서 도식상 ±1cm, B: 《针灸腧穴通考》가 고전 기술을 대추–견봉 중점으로 해석). 정본 Rank 5 분기 기준 미충족 → 단일 Target(고전=WHO)으로 조정하고 WHO 정위 채점(T2)을 최종값으로 채택. 참고: 고전 정위 별도 채점값 A 62.5/50/50/0, B 68.75/50/50/0. S_safety 0은 자침깊이 DB 동의보감 '0'(금침) 근거로 두 채점자 일치 → ⚠.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>단일 Target(고전=WHO, C7 극돌기–견봉 최외측점 중점)</t>
+          <t>Target 1≡2≡3 단일 Target(고전 문헌=촉진 실체화=WHO, C7 극돌기–견봉 최외측점 중점)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3978,267 +5123,6 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>없음</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>채점자 A</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>채점자 B</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>최종</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Layer B 참조 ID</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>papers.id</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>근거(A)</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>근거(B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>B1-01, B2-07, B2-09, B2-10</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1431, 1432, 1876</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>GB21 표준 위치의 사체 국소해부·초음파 심도 실측으로 등세모근·피신경·흉막 거리 확인.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2대 교재 공통 구조(등세모근·빗장위신경·등쪽어깨신경·가로목동정맥) + GB21 특이 국소해부·안전심도 실측.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>B1-03, B3-20</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>C3~C4 분절은 견항통과 정합, 난산·유옹과는 불일치.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>국소 견배통·경항강과 C3-C5 피절·근절 정합. 난산·乳痈 등 원격 주치와는 분절 불일치.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>B2-06, B3-06, B3-11</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>일반 구심 섬유 기전 유추.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>GB21 특이 구심 섬유·수용체 연구 없음, 일반 유추.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>B3-07, B3-08, B3-11</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>관문조절·DNIC 유추.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>일반 침 진통 중추 경로 유추.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>B2-03, B2-04, B2-06, B3-11</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>근막 이완·진통 방향은 견배통 주치와 일치(유추).</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>견배통 완화 방향은 유추로 일치. 난산 자궁수축 효과는 원심 경로 근거 없음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>B4-04, B4-05</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1874, 1884, 1891, 1893</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>혈류 pilot 1편 및 다혈 배오 RCT; 혈위 특이성 미확립.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>인체 관찰 1편과 다혈 배합 임상 RCT만 있어 혈위 특이 인체 전환 근거가 불충분.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>판정: 미부합</t>
         </is>
       </c>
     </row>
@@ -4253,337 +5137,307 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>papers.id</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>연도</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>저널</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>제목</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>PMID</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>DOI</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>설계</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>용도</t>
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>정의</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>원전 근거</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>X·Y 위치(체표)</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>자입 기준점</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>구판 표기 대응</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1876</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2004</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>J Tradit Chin Med</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Topography of acupoint Jianjing (GB 21).</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>15270272</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>인체 국소해부</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>① 실체·안전</t>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Target 1 (고전 문헌 위치)</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>최초 기술 문구 위치</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>《明堂》 在肩上陷解中，缺盆上大骨前(通考 名实考); 《甲乙》 在肩上陷者中(经络通鉴 11편 L984)</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>견상부, 缺盆 위·大骨(견갑극) 앞; 大骨前만으로 한 점 미정</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>v2.7 단일 Target(고전=WHO)의 고전 측 → Target 1≡2≡3</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1431</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Evid Based Complement Alternat Med</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Change of Safe Needling Depth at Acupoint GB21 according to Posture and Breathing</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10.1155/2018/2308102</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>해부·영상</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>① 실체·SI</t>
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Target 2 (촉진 실체화 위치)</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>촉진 표현이 가리키는 해부 공간</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>《圣惠》 以三指按之; 《卫生宝鉴》 以三指按取之，当其中指下陷中(证治 14편 L368); 《圣济总录》 膊骨罅…中指下即是; 《肘后》 两肩小近头凹处(证治 16편 L348)</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>등세모근(FMA:9626) 상연 위 체표 오목(陷中)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>간극 불명확 — 미표시(分肉·兩筋間·緣 기술 없음)</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>신규(2026-10-25)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1432</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Eur J Integr Med</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Determining maximal safe needling depth based on anthropometric measurements - Focusing on acupoint GB21</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10.1016/j.eujim.2018.05.006</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>해부·영상</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>① 실체·SI</t>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Target 3 (WHO 표준 위치)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>현대 표준 정위</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>WHO 2008(B1-05); 通考 提要</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>C7 극돌기–견봉 최외측점 중점</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>구판 v2.6 T2 "WHO 최고점" → Target 3; v2.7 채점 위치와 동일(점수 승계)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1896</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Integr Med Res</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Quantifying the therapeutic index of acupoints using measurements of effective and hazardous depths</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>42500462</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10.1016/j.imr.2026.101305</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>해부·영상</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SI 보조</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1874</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2007</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>J Altern Complement Med</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Noninvasive blood flow measurement over acupuncture points (Gb21): a pilot study.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>17309375</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10.1089/acm.2006.9149</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>인체 관찰(비RCT)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>⑥ / S_reflex</t>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>(폐기) 구판 v2.6 T1 "고전 오목점"</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>가공 인용 "古人取肩上陷者中, 今人取最高點…" 근거</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>구판 도식 후방 −1cm(구 T2와 약 20mm)</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>후보 제외(가공 인용·능형근 오기)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>1884</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Zhongguo Zhen Jiu</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Bloodletting at guasha marks combined with acupuncture for cervical spondylotic radiculopathy ...</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>41558700</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>10.13703/j.0255-2930.20241126-k0001</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>인체 RCT(다혈 배합)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>⑥ 보조</t>
-        </is>
-      </c>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>쌍</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Δ (추정)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>추정 근거</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>판정 (Δ &gt; 10mm 분기)</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>15mm→10mm 기준 변경 영향</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>1891</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Zhongguo Zhen Jiu</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Acupuncture and moxibustion based on meridian differentiation for cervical spondylosis radiculopathy ...</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>29231452</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>10.13703/j.0255-2930.2016.06.008</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>인체 RCT(다혈 배합)</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>⑥ 보조</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>T1–T2</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>≤ 10mm (추정)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>T1 문구 자체가 陷解中 촉진 표현 포함; T2는 같은 오목을 一寸半·三指法으로 고정</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>병합</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>변화 없음</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1893</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Zhen Ci Yan Jiu</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Randomized controlled trial on cervical spondylotic radiculopathy of wind-cold-damp type ...</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>34970881</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>10.13702/j.1000-0607.20210006</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>인체 RCT(다혈 배합)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>⑥ 보조</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>T1–T3</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>≤ 10mm (추정)</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>通考 名实考 실제 折量 = 肩髃–C7 중점</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>병합</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>변화 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>T2–T3</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>≤ 10mm (추정)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>通考 실측 해석(三指法·膊骨罅 = 중점); 肘后 小近头는 내측 치우침 시사하나 크기 미기재 — 경계 근처 가능성, 실측 없음</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>병합</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>변화 없음(경계 사례 주의)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Target 1≡2≡3 단일 Target — Rank 7 Tri-Target ΔARI 판정 대상 없음. 점수는 v2.7 이중 채점(A·B) 승계, 단일 채점(예비) Target 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>근거 포인터</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>通考(下)_241-320 名实考 L1249; data/classics/中国针灸证治通鉴/…_14_… L368, …_16_… L348; data/classics/中国针灸经络通鉴/…_11_… L984</t>
         </is>
       </c>
     </row>
